--- a/financial_model_15yr.xlsx
+++ b/financial_model_15yr.xlsx
@@ -3877,50 +3877,65 @@
           <t xml:space="preserve">    Paid-In Capital</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="C24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="H24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="K24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="L24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="N24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="O24" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="P24" s="21" t="n">
-        <v>25000</v>
+      <c r="B24" s="19">
+        <f>B12-B21-B25</f>
+        <v/>
+      </c>
+      <c r="C24" s="19">
+        <f>C12-C21-C25</f>
+        <v/>
+      </c>
+      <c r="D24" s="19">
+        <f>D12-D21-D25</f>
+        <v/>
+      </c>
+      <c r="E24" s="19">
+        <f>E12-E21-E25</f>
+        <v/>
+      </c>
+      <c r="F24" s="19">
+        <f>F12-F21-F25</f>
+        <v/>
+      </c>
+      <c r="G24" s="19">
+        <f>G12-G21-G25</f>
+        <v/>
+      </c>
+      <c r="H24" s="19">
+        <f>H12-H21-H25</f>
+        <v/>
+      </c>
+      <c r="I24" s="19">
+        <f>I12-I21-I25</f>
+        <v/>
+      </c>
+      <c r="J24" s="19">
+        <f>J12-J21-J25</f>
+        <v/>
+      </c>
+      <c r="K24" s="19">
+        <f>K12-K21-K25</f>
+        <v/>
+      </c>
+      <c r="L24" s="19">
+        <f>L12-L21-L25</f>
+        <v/>
+      </c>
+      <c r="M24" s="19">
+        <f>M12-M21-M25</f>
+        <v/>
+      </c>
+      <c r="N24" s="19">
+        <f>N12-N21-N25</f>
+        <v/>
+      </c>
+      <c r="O24" s="19">
+        <f>O12-O21-O25</f>
+        <v/>
+      </c>
+      <c r="P24" s="19">
+        <f>P12-P21-P25</f>
+        <v/>
       </c>
     </row>
     <row r="25">
